--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -712,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>599100</v>
+        <v>301800</v>
       </c>
       <c r="E8" s="3">
-        <v>584400</v>
+        <v>586000</v>
       </c>
       <c r="F8" s="3">
-        <v>575300</v>
+        <v>577000</v>
       </c>
       <c r="G8" s="3">
-        <v>961100</v>
+        <v>963800</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -772,10 +772,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>586000</v>
+        <v>288700</v>
       </c>
       <c r="E10" s="3">
-        <v>582600</v>
+        <v>584300</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -816,16 +816,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>479000</v>
+        <v>237500</v>
       </c>
       <c r="E12" s="3">
-        <v>495000</v>
+        <v>496400</v>
       </c>
       <c r="F12" s="3">
-        <v>540800</v>
+        <v>542300</v>
       </c>
       <c r="G12" s="3">
-        <v>429700</v>
+        <v>430900</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -876,7 +876,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>29000</v>
+        <v>29100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -906,16 +906,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>42200</v>
+        <v>98300</v>
       </c>
       <c r="E15" s="3">
-        <v>37600</v>
+        <v>37700</v>
       </c>
       <c r="F15" s="3">
-        <v>18400</v>
+        <v>18500</v>
       </c>
       <c r="G15" s="3">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -947,16 +947,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>889300</v>
+        <v>444400</v>
       </c>
       <c r="E17" s="3">
-        <v>764000</v>
+        <v>766200</v>
       </c>
       <c r="F17" s="3">
-        <v>769100</v>
+        <v>771300</v>
       </c>
       <c r="G17" s="3">
-        <v>561000</v>
+        <v>562600</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -977,16 +977,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-290300</v>
+        <v>-142600</v>
       </c>
       <c r="E18" s="3">
-        <v>-179700</v>
+        <v>-180200</v>
       </c>
       <c r="F18" s="3">
-        <v>-193800</v>
+        <v>-194400</v>
       </c>
       <c r="G18" s="3">
-        <v>400100</v>
+        <v>401200</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1021,16 +1021,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>64400</v>
+        <v>73100</v>
       </c>
       <c r="E20" s="3">
-        <v>58900</v>
+        <v>59000</v>
       </c>
       <c r="F20" s="3">
-        <v>-132100</v>
+        <v>-132500</v>
       </c>
       <c r="G20" s="3">
-        <v>-237600</v>
+        <v>-238200</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1051,16 +1051,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-154800</v>
+        <v>2300</v>
       </c>
       <c r="E21" s="3">
         <v>-83200</v>
       </c>
       <c r="F21" s="3">
-        <v>-305700</v>
+        <v>-306400</v>
       </c>
       <c r="G21" s="3">
-        <v>176000</v>
+        <v>176600</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1084,7 +1084,7 @@
         <v>7600</v>
       </c>
       <c r="E22" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="F22" s="3">
         <v>10200</v>
@@ -1111,16 +1111,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-233400</v>
+        <v>-77100</v>
       </c>
       <c r="E23" s="3">
-        <v>-133500</v>
+        <v>-133800</v>
       </c>
       <c r="F23" s="3">
-        <v>-336100</v>
+        <v>-337100</v>
       </c>
       <c r="G23" s="3">
-        <v>161100</v>
+        <v>161600</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1141,7 +1141,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3100</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>2600</v>
@@ -1201,16 +1201,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-236500</v>
+        <v>-77700</v>
       </c>
       <c r="E26" s="3">
-        <v>-136100</v>
+        <v>-136500</v>
       </c>
       <c r="F26" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="G26" s="3">
-        <v>161300</v>
+        <v>161800</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-236500</v>
+        <v>-77700</v>
       </c>
       <c r="E27" s="3">
-        <v>-136100</v>
+        <v>-136500</v>
       </c>
       <c r="F27" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="G27" s="3">
-        <v>161300</v>
+        <v>161800</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1291,13 +1291,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-159500</v>
       </c>
       <c r="E29" s="3">
         <v>24100</v>
       </c>
       <c r="F29" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="G29" s="3">
         <v>1300</v>
@@ -1381,16 +1381,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-64400</v>
+        <v>-73100</v>
       </c>
       <c r="E32" s="3">
-        <v>-58900</v>
+        <v>-59000</v>
       </c>
       <c r="F32" s="3">
-        <v>132100</v>
+        <v>132500</v>
       </c>
       <c r="G32" s="3">
-        <v>237600</v>
+        <v>238200</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1411,16 +1411,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-236500</v>
+        <v>-237200</v>
       </c>
       <c r="E33" s="3">
-        <v>-112000</v>
+        <v>-112300</v>
       </c>
       <c r="F33" s="3">
-        <v>-331400</v>
+        <v>-332300</v>
       </c>
       <c r="G33" s="3">
-        <v>162600</v>
+        <v>163000</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1471,16 +1471,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-236500</v>
+        <v>-237200</v>
       </c>
       <c r="E35" s="3">
-        <v>-112000</v>
+        <v>-112300</v>
       </c>
       <c r="F35" s="3">
-        <v>-331400</v>
+        <v>-332300</v>
       </c>
       <c r="G35" s="3">
-        <v>162600</v>
+        <v>163000</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1564,16 +1564,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>497100</v>
+        <v>498500</v>
       </c>
       <c r="E41" s="3">
-        <v>1330100</v>
+        <v>1333900</v>
       </c>
       <c r="F41" s="3">
-        <v>1345400</v>
+        <v>1349200</v>
       </c>
       <c r="G41" s="3">
-        <v>985100</v>
+        <v>987900</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1594,16 +1594,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3945000</v>
+        <v>3956300</v>
       </c>
       <c r="E42" s="3">
-        <v>3772900</v>
+        <v>3783700</v>
       </c>
       <c r="F42" s="3">
-        <v>4254800</v>
+        <v>4267000</v>
       </c>
       <c r="G42" s="3">
-        <v>5287100</v>
+        <v>5302200</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1624,16 +1624,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>83900</v>
+        <v>84200</v>
       </c>
       <c r="E43" s="3">
-        <v>139500</v>
+        <v>139900</v>
       </c>
       <c r="F43" s="3">
-        <v>188100</v>
+        <v>188700</v>
       </c>
       <c r="G43" s="3">
-        <v>86900</v>
+        <v>87200</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1654,10 +1654,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>57400</v>
+        <v>57600</v>
       </c>
       <c r="E44" s="3">
-        <v>22300</v>
+        <v>22400</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
@@ -1690,7 +1690,7 @@
         <v>10300</v>
       </c>
       <c r="F45" s="3">
-        <v>37000</v>
+        <v>37100</v>
       </c>
       <c r="G45" s="3">
         <v>5100</v>
@@ -1714,16 +1714,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4597000</v>
+        <v>4610100</v>
       </c>
       <c r="E46" s="3">
-        <v>5275100</v>
+        <v>5290200</v>
       </c>
       <c r="F46" s="3">
-        <v>5825700</v>
+        <v>5842400</v>
       </c>
       <c r="G46" s="3">
-        <v>6364500</v>
+        <v>6382700</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1744,16 +1744,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>130100</v>
+        <v>130500</v>
       </c>
       <c r="E47" s="3">
-        <v>138000</v>
+        <v>138400</v>
       </c>
       <c r="F47" s="3">
-        <v>175400</v>
+        <v>175900</v>
       </c>
       <c r="G47" s="3">
-        <v>101300</v>
+        <v>101600</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1774,16 +1774,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>167400</v>
+        <v>167800</v>
       </c>
       <c r="E48" s="3">
-        <v>149200</v>
+        <v>149600</v>
       </c>
       <c r="F48" s="3">
-        <v>112200</v>
+        <v>112500</v>
       </c>
       <c r="G48" s="3">
-        <v>71700</v>
+        <v>71900</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1804,16 +1804,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>234500</v>
+        <v>235200</v>
       </c>
       <c r="E49" s="3">
-        <v>65200</v>
+        <v>65400</v>
       </c>
       <c r="F49" s="3">
-        <v>73300</v>
+        <v>73500</v>
       </c>
       <c r="G49" s="3">
-        <v>27000</v>
+        <v>27100</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1894,7 +1894,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="E52" s="3">
         <v>7100</v>
@@ -1954,16 +1954,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5136800</v>
+        <v>5151400</v>
       </c>
       <c r="E54" s="3">
-        <v>5634600</v>
+        <v>5650700</v>
       </c>
       <c r="F54" s="3">
-        <v>6203700</v>
+        <v>6221500</v>
       </c>
       <c r="G54" s="3">
-        <v>6584400</v>
+        <v>6603300</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2012,16 +2012,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>160600</v>
+        <v>161000</v>
       </c>
       <c r="E57" s="3">
-        <v>149100</v>
+        <v>149500</v>
       </c>
       <c r="F57" s="3">
-        <v>187000</v>
+        <v>187600</v>
       </c>
       <c r="G57" s="3">
-        <v>155600</v>
+        <v>156100</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2048,7 +2048,7 @@
         <v>7800</v>
       </c>
       <c r="F58" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="3">
         <v>6300</v>
@@ -2072,16 +2072,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>398500</v>
+        <v>399700</v>
       </c>
       <c r="E59" s="3">
-        <v>457700</v>
+        <v>459000</v>
       </c>
       <c r="F59" s="3">
-        <v>495300</v>
+        <v>496700</v>
       </c>
       <c r="G59" s="3">
-        <v>458400</v>
+        <v>459800</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2102,16 +2102,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>567000</v>
+        <v>568600</v>
       </c>
       <c r="E60" s="3">
-        <v>614600</v>
+        <v>616400</v>
       </c>
       <c r="F60" s="3">
-        <v>689300</v>
+        <v>691200</v>
       </c>
       <c r="G60" s="3">
-        <v>620400</v>
+        <v>622200</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2132,16 +2132,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="E61" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F61" s="3">
+        <v>25100</v>
+      </c>
+      <c r="G61" s="3">
         <v>21300</v>
-      </c>
-      <c r="F61" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>21200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2162,16 +2162,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1813100</v>
+        <v>1818300</v>
       </c>
       <c r="E62" s="3">
-        <v>2130600</v>
+        <v>2136700</v>
       </c>
       <c r="F62" s="3">
-        <v>2592100</v>
+        <v>2599500</v>
       </c>
       <c r="G62" s="3">
-        <v>2822700</v>
+        <v>2830800</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2282,16 +2282,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2396000</v>
+        <v>2402900</v>
       </c>
       <c r="E66" s="3">
-        <v>2766500</v>
+        <v>2774400</v>
       </c>
       <c r="F66" s="3">
-        <v>3306400</v>
+        <v>3315800</v>
       </c>
       <c r="G66" s="3">
-        <v>3464400</v>
+        <v>3474200</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2446,16 +2446,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-544200</v>
+        <v>-545700</v>
       </c>
       <c r="E72" s="3">
-        <v>-409500</v>
+        <v>-410600</v>
       </c>
       <c r="F72" s="3">
-        <v>-375000</v>
+        <v>-376100</v>
       </c>
       <c r="G72" s="3">
-        <v>-123800</v>
+        <v>-124100</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2566,16 +2566,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2740700</v>
+        <v>2748600</v>
       </c>
       <c r="E76" s="3">
-        <v>2868000</v>
+        <v>2876200</v>
       </c>
       <c r="F76" s="3">
-        <v>2897300</v>
+        <v>2905600</v>
       </c>
       <c r="G76" s="3">
-        <v>3120100</v>
+        <v>3129000</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2661,16 +2661,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-236500</v>
+        <v>-237200</v>
       </c>
       <c r="E81" s="3">
-        <v>-112000</v>
+        <v>-112300</v>
       </c>
       <c r="F81" s="3">
-        <v>-331400</v>
+        <v>-332300</v>
       </c>
       <c r="G81" s="3">
-        <v>162600</v>
+        <v>163000</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2705,10 +2705,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>71100</v>
+        <v>71300</v>
       </c>
       <c r="E83" s="3">
-        <v>37600</v>
+        <v>37700</v>
       </c>
       <c r="F83" s="3">
         <v>20300</v>
@@ -2885,16 +2885,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-543100</v>
+        <v>-544600</v>
       </c>
       <c r="E89" s="3">
-        <v>-546700</v>
+        <v>-548200</v>
       </c>
       <c r="F89" s="3">
-        <v>-463700</v>
+        <v>-465000</v>
       </c>
       <c r="G89" s="3">
-        <v>3265500</v>
+        <v>3274800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2929,16 +2929,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29700</v>
+        <v>-29800</v>
       </c>
       <c r="E91" s="3">
-        <v>-58800</v>
+        <v>-59000</v>
       </c>
       <c r="F91" s="3">
-        <v>-46100</v>
+        <v>-46300</v>
       </c>
       <c r="G91" s="3">
-        <v>-24300</v>
+        <v>-24400</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3019,16 +3019,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1351400</v>
+        <v>-1355200</v>
       </c>
       <c r="E94" s="3">
-        <v>587200</v>
+        <v>588900</v>
       </c>
       <c r="F94" s="3">
-        <v>821700</v>
+        <v>824000</v>
       </c>
       <c r="G94" s="3">
-        <v>-4084700</v>
+        <v>-4096300</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3189,10 +3189,10 @@
         <v>-4200</v>
       </c>
       <c r="F100" s="3">
-        <v>23900</v>
+        <v>24000</v>
       </c>
       <c r="G100" s="3">
-        <v>1449300</v>
+        <v>1453400</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3213,13 +3213,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>24200</v>
+        <v>24300</v>
       </c>
       <c r="E101" s="3">
-        <v>61600</v>
+        <v>61800</v>
       </c>
       <c r="F101" s="3">
-        <v>-76500</v>
+        <v>-76800</v>
       </c>
       <c r="G101" s="3">
         <v>-10800</v>
@@ -3243,16 +3243,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1871900</v>
+        <v>-1877200</v>
       </c>
       <c r="E102" s="3">
-        <v>98000</v>
+        <v>98300</v>
       </c>
       <c r="F102" s="3">
-        <v>305400</v>
+        <v>306200</v>
       </c>
       <c r="G102" s="3">
-        <v>619300</v>
+        <v>621100</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>GLPG</t>
   </si>
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,26 +705,29 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>301800</v>
+        <v>310200</v>
       </c>
       <c r="E8" s="3">
-        <v>586000</v>
+        <v>299800</v>
       </c>
       <c r="F8" s="3">
-        <v>577000</v>
+        <v>582100</v>
       </c>
       <c r="G8" s="3">
-        <v>963800</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+        <v>573100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>957300</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -735,21 +738,24 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>13100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1800</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,20 +771,23 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>288700</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>584300</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>286700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>580300</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,25 +822,26 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>237500</v>
+        <v>198700</v>
       </c>
       <c r="E12" s="3">
-        <v>496400</v>
+        <v>193300</v>
       </c>
       <c r="F12" s="3">
-        <v>542300</v>
+        <v>493000</v>
       </c>
       <c r="G12" s="3">
-        <v>430900</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
+        <v>538600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>428000</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,17 +885,20 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>29100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>24100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>28900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -896,29 +915,32 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>98300</v>
+        <v>41400</v>
       </c>
       <c r="E15" s="3">
-        <v>37700</v>
+        <v>94900</v>
       </c>
       <c r="F15" s="3">
-        <v>18500</v>
+        <v>37400</v>
       </c>
       <c r="G15" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+        <v>18400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>11700</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -929,9 +951,12 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,25 +966,26 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>444400</v>
+        <v>405500</v>
       </c>
       <c r="E17" s="3">
-        <v>766200</v>
+        <v>441400</v>
       </c>
       <c r="F17" s="3">
-        <v>771300</v>
+        <v>761000</v>
       </c>
       <c r="G17" s="3">
-        <v>562600</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+        <v>766100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>558800</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -970,26 +996,29 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-142600</v>
+        <v>-95400</v>
       </c>
       <c r="E18" s="3">
-        <v>-180200</v>
+        <v>-141600</v>
       </c>
       <c r="F18" s="3">
-        <v>-194400</v>
+        <v>-179000</v>
       </c>
       <c r="G18" s="3">
-        <v>401200</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>-193000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>398500</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,25 +1047,26 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>73100</v>
+        <v>103400</v>
       </c>
       <c r="E20" s="3">
-        <v>59000</v>
+        <v>72500</v>
       </c>
       <c r="F20" s="3">
-        <v>-132500</v>
+        <v>58600</v>
       </c>
       <c r="G20" s="3">
-        <v>-238200</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>-131600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-236600</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1044,26 +1077,29 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2300</v>
+        <v>54900</v>
       </c>
       <c r="E21" s="3">
-        <v>-83200</v>
+        <v>1300</v>
       </c>
       <c r="F21" s="3">
-        <v>-306400</v>
+        <v>-83100</v>
       </c>
       <c r="G21" s="3">
-        <v>176600</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>-304600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>175200</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1074,27 +1110,30 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7600</v>
+        <v>1900</v>
       </c>
       <c r="E22" s="3">
-        <v>12700</v>
+        <v>7400</v>
       </c>
       <c r="F22" s="3">
-        <v>10200</v>
+        <v>12600</v>
       </c>
       <c r="G22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,26 +1143,29 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-77100</v>
+        <v>6100</v>
       </c>
       <c r="E23" s="3">
-        <v>-133800</v>
+        <v>-76600</v>
       </c>
       <c r="F23" s="3">
-        <v>-337100</v>
+        <v>-132900</v>
       </c>
       <c r="G23" s="3">
-        <v>161600</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+        <v>-334800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>160500</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1134,27 +1176,30 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,26 +1242,29 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-77700</v>
+        <v>-4300</v>
       </c>
       <c r="E26" s="3">
-        <v>-136500</v>
+        <v>-77200</v>
       </c>
       <c r="F26" s="3">
-        <v>-338400</v>
+        <v>-135500</v>
       </c>
       <c r="G26" s="3">
-        <v>161800</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+        <v>-336100</v>
+      </c>
+      <c r="H26" s="3">
+        <v>160700</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1224,26 +1275,29 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-77700</v>
+        <v>-4300</v>
       </c>
       <c r="E27" s="3">
-        <v>-136500</v>
+        <v>-77200</v>
       </c>
       <c r="F27" s="3">
-        <v>-338400</v>
+        <v>-135500</v>
       </c>
       <c r="G27" s="3">
-        <v>161800</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+        <v>-336100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>160700</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,26 +1341,29 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-159500</v>
+        <v>233100</v>
       </c>
       <c r="E29" s="3">
-        <v>24100</v>
+        <v>-158400</v>
       </c>
       <c r="F29" s="3">
-        <v>6100</v>
+        <v>24000</v>
       </c>
       <c r="G29" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
+        <v>6000</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1200</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,26 +1440,29 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-73100</v>
+        <v>-103400</v>
       </c>
       <c r="E32" s="3">
-        <v>-59000</v>
+        <v>-72500</v>
       </c>
       <c r="F32" s="3">
-        <v>132500</v>
+        <v>-58600</v>
       </c>
       <c r="G32" s="3">
-        <v>238200</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>131600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>236600</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1404,26 +1473,29 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-237200</v>
+        <v>228800</v>
       </c>
       <c r="E33" s="3">
-        <v>-112300</v>
+        <v>-235600</v>
       </c>
       <c r="F33" s="3">
-        <v>-332300</v>
+        <v>-111600</v>
       </c>
       <c r="G33" s="3">
-        <v>163000</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+        <v>-330100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>161900</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,26 +1539,29 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-237200</v>
+        <v>228800</v>
       </c>
       <c r="E35" s="3">
-        <v>-112300</v>
+        <v>-235600</v>
       </c>
       <c r="F35" s="3">
-        <v>-332300</v>
+        <v>-111600</v>
       </c>
       <c r="G35" s="3">
-        <v>163000</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+        <v>-330100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>161900</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1494,32 +1572,35 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,25 +1643,26 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>498500</v>
+        <v>77600</v>
       </c>
       <c r="E41" s="3">
-        <v>1333900</v>
+        <v>495100</v>
       </c>
       <c r="F41" s="3">
-        <v>1349200</v>
+        <v>1324800</v>
       </c>
       <c r="G41" s="3">
-        <v>987900</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+        <v>1340100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>981200</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1587,26 +1673,29 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3956300</v>
+        <v>3904200</v>
       </c>
       <c r="E42" s="3">
-        <v>3783700</v>
+        <v>3929400</v>
       </c>
       <c r="F42" s="3">
-        <v>4267000</v>
+        <v>3757900</v>
       </c>
       <c r="G42" s="3">
-        <v>5302200</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+        <v>4237900</v>
+      </c>
+      <c r="H42" s="3">
+        <v>5266100</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1617,26 +1706,29 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>84200</v>
+        <v>71000</v>
       </c>
       <c r="E43" s="3">
-        <v>139900</v>
+        <v>83600</v>
       </c>
       <c r="F43" s="3">
-        <v>188700</v>
+        <v>139000</v>
       </c>
       <c r="G43" s="3">
-        <v>87200</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>187400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>86600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1647,27 +1739,30 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>57600</v>
+        <v>79900</v>
       </c>
       <c r="E44" s="3">
-        <v>22400</v>
+        <v>57200</v>
       </c>
       <c r="F44" s="3">
+        <v>22200</v>
+      </c>
+      <c r="G44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,27 +1772,30 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13600</v>
+        <v>40500</v>
       </c>
       <c r="E45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F45" s="3">
         <v>10300</v>
       </c>
-      <c r="F45" s="3">
-        <v>37100</v>
-      </c>
       <c r="G45" s="3">
+        <v>36900</v>
+      </c>
+      <c r="H45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1707,26 +1805,29 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4610100</v>
+        <v>4173200</v>
       </c>
       <c r="E46" s="3">
-        <v>5290200</v>
+        <v>4578800</v>
       </c>
       <c r="F46" s="3">
-        <v>5842400</v>
+        <v>5254200</v>
       </c>
       <c r="G46" s="3">
-        <v>6382700</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+        <v>5802700</v>
+      </c>
+      <c r="H46" s="3">
+        <v>6339300</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1737,26 +1838,29 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>130500</v>
+        <v>152700</v>
       </c>
       <c r="E47" s="3">
-        <v>138400</v>
+        <v>129600</v>
       </c>
       <c r="F47" s="3">
-        <v>175900</v>
+        <v>137400</v>
       </c>
       <c r="G47" s="3">
-        <v>101600</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+        <v>174700</v>
+      </c>
+      <c r="H47" s="3">
+        <v>100900</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1767,26 +1871,29 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>167800</v>
+        <v>136500</v>
       </c>
       <c r="E48" s="3">
-        <v>149600</v>
+        <v>166700</v>
       </c>
       <c r="F48" s="3">
-        <v>112500</v>
+        <v>148600</v>
       </c>
       <c r="G48" s="3">
-        <v>71900</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+        <v>111700</v>
+      </c>
+      <c r="H48" s="3">
+        <v>71400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1797,26 +1904,29 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>235200</v>
+        <v>213400</v>
       </c>
       <c r="E49" s="3">
-        <v>65400</v>
+        <v>233600</v>
       </c>
       <c r="F49" s="3">
-        <v>73500</v>
+        <v>65000</v>
       </c>
       <c r="G49" s="3">
-        <v>27100</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+        <v>73000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>26900</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,26 +2003,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7800</v>
+        <v>33300</v>
       </c>
       <c r="E52" s="3">
-        <v>7100</v>
+        <v>7700</v>
       </c>
       <c r="F52" s="3">
-        <v>17200</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="3">
-        <v>19900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>17100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>19800</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,26 +2069,29 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5151400</v>
+        <v>4709000</v>
       </c>
       <c r="E54" s="3">
-        <v>5650700</v>
+        <v>5116400</v>
       </c>
       <c r="F54" s="3">
-        <v>6221500</v>
+        <v>5612200</v>
       </c>
       <c r="G54" s="3">
-        <v>6603300</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+        <v>6179200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>6558300</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,25 +2135,26 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>161000</v>
+        <v>145500</v>
       </c>
       <c r="E57" s="3">
-        <v>149500</v>
+        <v>159900</v>
       </c>
       <c r="F57" s="3">
-        <v>187600</v>
+        <v>148500</v>
       </c>
       <c r="G57" s="3">
-        <v>156100</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+        <v>186300</v>
+      </c>
+      <c r="H57" s="3">
+        <v>155000</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2035,27 +2165,30 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7800</v>
+        <v>5000</v>
       </c>
       <c r="E58" s="3">
         <v>7800</v>
       </c>
       <c r="F58" s="3">
-        <v>7000</v>
+        <v>7800</v>
       </c>
       <c r="G58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H58" s="3">
         <v>6300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2065,26 +2198,29 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>399700</v>
+        <v>312200</v>
       </c>
       <c r="E59" s="3">
-        <v>459000</v>
+        <v>397000</v>
       </c>
       <c r="F59" s="3">
-        <v>496700</v>
+        <v>455900</v>
       </c>
       <c r="G59" s="3">
-        <v>459800</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>493300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>456600</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2095,26 +2231,29 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>568600</v>
+        <v>462800</v>
       </c>
       <c r="E60" s="3">
-        <v>616400</v>
+        <v>564700</v>
       </c>
       <c r="F60" s="3">
-        <v>691200</v>
+        <v>612200</v>
       </c>
       <c r="G60" s="3">
-        <v>622200</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+        <v>686500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>617900</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2125,26 +2264,29 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16000</v>
+        <v>5300</v>
       </c>
       <c r="E61" s="3">
-        <v>21400</v>
+        <v>15900</v>
       </c>
       <c r="F61" s="3">
-        <v>25100</v>
+        <v>21200</v>
       </c>
       <c r="G61" s="3">
-        <v>21300</v>
+        <v>24900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2155,26 +2297,29 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1818300</v>
+        <v>1219700</v>
       </c>
       <c r="E62" s="3">
-        <v>2136700</v>
+        <v>1806000</v>
       </c>
       <c r="F62" s="3">
-        <v>2599500</v>
+        <v>2122100</v>
       </c>
       <c r="G62" s="3">
-        <v>2830800</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>2581900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2811500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,26 +2429,29 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2402900</v>
+        <v>1687900</v>
       </c>
       <c r="E66" s="3">
-        <v>2774400</v>
+        <v>2386500</v>
       </c>
       <c r="F66" s="3">
-        <v>3315800</v>
+        <v>2755600</v>
       </c>
       <c r="G66" s="3">
-        <v>3474200</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+        <v>3293300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>3450600</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,26 +2609,29 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-545700</v>
+        <v>-253100</v>
       </c>
       <c r="E72" s="3">
-        <v>-410600</v>
+        <v>-542000</v>
       </c>
       <c r="F72" s="3">
-        <v>-376100</v>
+        <v>-407800</v>
       </c>
       <c r="G72" s="3">
-        <v>-124100</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+        <v>-373500</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-123300</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,26 +2741,29 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2748600</v>
+        <v>3021200</v>
       </c>
       <c r="E76" s="3">
-        <v>2876200</v>
+        <v>2729900</v>
       </c>
       <c r="F76" s="3">
-        <v>2905600</v>
+        <v>2856700</v>
       </c>
       <c r="G76" s="3">
-        <v>3129000</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+        <v>2885900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>3107700</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,32 +2807,35 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,26 +2845,29 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-237200</v>
+        <v>228800</v>
       </c>
       <c r="E81" s="3">
-        <v>-112300</v>
+        <v>-235600</v>
       </c>
       <c r="F81" s="3">
-        <v>-332300</v>
+        <v>-111600</v>
       </c>
       <c r="G81" s="3">
-        <v>163000</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+        <v>-330100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>161900</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,26 +2896,27 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>71300</v>
+        <v>47200</v>
       </c>
       <c r="E83" s="3">
-        <v>37700</v>
+        <v>70900</v>
       </c>
       <c r="F83" s="3">
-        <v>20300</v>
+        <v>37400</v>
       </c>
       <c r="G83" s="3">
+        <v>20200</v>
+      </c>
+      <c r="H83" s="3">
         <v>13500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2728,9 +2926,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,26 +3091,29 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-544600</v>
+        <v>-438700</v>
       </c>
       <c r="E89" s="3">
-        <v>-548200</v>
+        <v>-540900</v>
       </c>
       <c r="F89" s="3">
-        <v>-465000</v>
+        <v>-544500</v>
       </c>
       <c r="G89" s="3">
-        <v>3274800</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>-461800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>3252600</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,25 +3142,26 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29800</v>
+        <v>-20200</v>
       </c>
       <c r="E91" s="3">
-        <v>-59000</v>
+        <v>-29600</v>
       </c>
       <c r="F91" s="3">
-        <v>-46300</v>
+        <v>-58600</v>
       </c>
       <c r="G91" s="3">
-        <v>-24400</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+        <v>-46000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-24200</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,26 +3238,29 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1355200</v>
+        <v>76900</v>
       </c>
       <c r="E94" s="3">
-        <v>588900</v>
+        <v>-1346000</v>
       </c>
       <c r="F94" s="3">
-        <v>824000</v>
+        <v>584900</v>
       </c>
       <c r="G94" s="3">
-        <v>-4096300</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+        <v>818400</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-4068500</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,26 +3418,29 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4200</v>
       </c>
-      <c r="F100" s="3">
-        <v>24000</v>
-      </c>
       <c r="G100" s="3">
-        <v>1453400</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+        <v>23800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1443500</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3206,27 +3451,30 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>24300</v>
+        <v>-1600</v>
       </c>
       <c r="E101" s="3">
-        <v>61800</v>
+        <v>24100</v>
       </c>
       <c r="F101" s="3">
-        <v>-76800</v>
+        <v>61300</v>
       </c>
       <c r="G101" s="3">
+        <v>-76200</v>
+      </c>
+      <c r="H101" s="3">
         <v>-10800</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3236,26 +3484,29 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1877200</v>
+        <v>-368900</v>
       </c>
       <c r="E102" s="3">
-        <v>98300</v>
+        <v>-1864500</v>
       </c>
       <c r="F102" s="3">
-        <v>306200</v>
+        <v>97600</v>
       </c>
       <c r="G102" s="3">
-        <v>621100</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+        <v>304200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>616900</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -715,19 +715,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>310200</v>
+        <v>317900</v>
       </c>
       <c r="E8" s="3">
-        <v>299800</v>
+        <v>307200</v>
       </c>
       <c r="F8" s="3">
-        <v>582100</v>
+        <v>596500</v>
       </c>
       <c r="G8" s="3">
-        <v>573100</v>
+        <v>587300</v>
       </c>
       <c r="H8" s="3">
-        <v>957300</v>
+        <v>981100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="3">
-        <v>13100</v>
+        <v>13400</v>
       </c>
       <c r="F9" s="3">
         <v>1800</v>
@@ -784,10 +784,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>286700</v>
+        <v>293800</v>
       </c>
       <c r="F10" s="3">
-        <v>580300</v>
+        <v>594700</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -829,19 +829,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>198700</v>
+        <v>203600</v>
       </c>
       <c r="E12" s="3">
-        <v>193300</v>
+        <v>198100</v>
       </c>
       <c r="F12" s="3">
-        <v>493000</v>
+        <v>505300</v>
       </c>
       <c r="G12" s="3">
-        <v>538600</v>
+        <v>552000</v>
       </c>
       <c r="H12" s="3">
-        <v>428000</v>
+        <v>438600</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24100</v>
+        <v>24700</v>
       </c>
       <c r="E14" s="3">
-        <v>28900</v>
+        <v>29600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -928,19 +928,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>41400</v>
+        <v>42500</v>
       </c>
       <c r="E15" s="3">
-        <v>94900</v>
+        <v>97300</v>
       </c>
       <c r="F15" s="3">
-        <v>37400</v>
+        <v>38400</v>
       </c>
       <c r="G15" s="3">
-        <v>18400</v>
+        <v>18800</v>
       </c>
       <c r="H15" s="3">
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -973,19 +973,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>405500</v>
+        <v>415600</v>
       </c>
       <c r="E17" s="3">
-        <v>441400</v>
+        <v>452400</v>
       </c>
       <c r="F17" s="3">
-        <v>761000</v>
+        <v>780000</v>
       </c>
       <c r="G17" s="3">
-        <v>766100</v>
+        <v>785200</v>
       </c>
       <c r="H17" s="3">
-        <v>558800</v>
+        <v>572700</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1006,19 +1006,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-95400</v>
+        <v>-97800</v>
       </c>
       <c r="E18" s="3">
-        <v>-141600</v>
+        <v>-145200</v>
       </c>
       <c r="F18" s="3">
-        <v>-179000</v>
+        <v>-183400</v>
       </c>
       <c r="G18" s="3">
-        <v>-193000</v>
+        <v>-197900</v>
       </c>
       <c r="H18" s="3">
-        <v>398500</v>
+        <v>408400</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1054,19 +1054,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>103400</v>
+        <v>106000</v>
       </c>
       <c r="E20" s="3">
-        <v>72500</v>
+        <v>74300</v>
       </c>
       <c r="F20" s="3">
-        <v>58600</v>
+        <v>60100</v>
       </c>
       <c r="G20" s="3">
-        <v>-131600</v>
+        <v>-134900</v>
       </c>
       <c r="H20" s="3">
-        <v>-236600</v>
+        <v>-242500</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1087,19 +1087,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>54900</v>
+        <v>56500</v>
       </c>
       <c r="E21" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="F21" s="3">
-        <v>-83100</v>
+        <v>-85000</v>
       </c>
       <c r="G21" s="3">
-        <v>-304600</v>
+        <v>-312000</v>
       </c>
       <c r="H21" s="3">
-        <v>175200</v>
+        <v>179700</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1120,16 +1120,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="F22" s="3">
-        <v>12600</v>
+        <v>12900</v>
       </c>
       <c r="G22" s="3">
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="H22" s="3">
         <v>1400</v>
@@ -1153,19 +1153,19 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="E23" s="3">
-        <v>-76600</v>
+        <v>-78500</v>
       </c>
       <c r="F23" s="3">
-        <v>-132900</v>
+        <v>-136200</v>
       </c>
       <c r="G23" s="3">
-        <v>-334800</v>
+        <v>-343100</v>
       </c>
       <c r="H23" s="3">
-        <v>160500</v>
+        <v>164500</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1186,16 +1186,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>10400</v>
+        <v>10600</v>
       </c>
       <c r="E24" s="3">
         <v>600</v>
       </c>
       <c r="F24" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G24" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H24" s="3">
         <v>-200</v>
@@ -1252,19 +1252,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-77200</v>
+        <v>-79100</v>
       </c>
       <c r="F26" s="3">
-        <v>-135500</v>
+        <v>-138900</v>
       </c>
       <c r="G26" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="H26" s="3">
-        <v>160700</v>
+        <v>164700</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1285,19 +1285,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E27" s="3">
-        <v>-77200</v>
+        <v>-79100</v>
       </c>
       <c r="F27" s="3">
-        <v>-135500</v>
+        <v>-138900</v>
       </c>
       <c r="G27" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="H27" s="3">
-        <v>160700</v>
+        <v>164700</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1351,19 +1351,19 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>233100</v>
+        <v>238900</v>
       </c>
       <c r="E29" s="3">
-        <v>-158400</v>
+        <v>-162300</v>
       </c>
       <c r="F29" s="3">
-        <v>24000</v>
+        <v>24600</v>
       </c>
       <c r="G29" s="3">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="H29" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
@@ -1450,19 +1450,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-103400</v>
+        <v>-106000</v>
       </c>
       <c r="E32" s="3">
-        <v>-72500</v>
+        <v>-74300</v>
       </c>
       <c r="F32" s="3">
-        <v>-58600</v>
+        <v>-60100</v>
       </c>
       <c r="G32" s="3">
-        <v>131600</v>
+        <v>134900</v>
       </c>
       <c r="H32" s="3">
-        <v>236600</v>
+        <v>242500</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1483,19 +1483,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>228800</v>
+        <v>234500</v>
       </c>
       <c r="E33" s="3">
-        <v>-235600</v>
+        <v>-241400</v>
       </c>
       <c r="F33" s="3">
-        <v>-111600</v>
+        <v>-114300</v>
       </c>
       <c r="G33" s="3">
-        <v>-330100</v>
+        <v>-338300</v>
       </c>
       <c r="H33" s="3">
-        <v>161900</v>
+        <v>166000</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1549,19 +1549,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>228800</v>
+        <v>234500</v>
       </c>
       <c r="E35" s="3">
-        <v>-235600</v>
+        <v>-241400</v>
       </c>
       <c r="F35" s="3">
-        <v>-111600</v>
+        <v>-114300</v>
       </c>
       <c r="G35" s="3">
-        <v>-330100</v>
+        <v>-338300</v>
       </c>
       <c r="H35" s="3">
-        <v>161900</v>
+        <v>166000</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1650,19 +1650,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>77600</v>
+        <v>79500</v>
       </c>
       <c r="E41" s="3">
-        <v>495100</v>
+        <v>507400</v>
       </c>
       <c r="F41" s="3">
-        <v>1324800</v>
+        <v>1357800</v>
       </c>
       <c r="G41" s="3">
-        <v>1340100</v>
+        <v>1373400</v>
       </c>
       <c r="H41" s="3">
-        <v>981200</v>
+        <v>1005600</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1683,19 +1683,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3904200</v>
+        <v>4001400</v>
       </c>
       <c r="E42" s="3">
-        <v>3929400</v>
+        <v>4027200</v>
       </c>
       <c r="F42" s="3">
-        <v>3757900</v>
+        <v>3851500</v>
       </c>
       <c r="G42" s="3">
-        <v>4237900</v>
+        <v>4343400</v>
       </c>
       <c r="H42" s="3">
-        <v>5266100</v>
+        <v>5397200</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1716,19 +1716,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>71000</v>
+        <v>72700</v>
       </c>
       <c r="E43" s="3">
-        <v>83600</v>
+        <v>85700</v>
       </c>
       <c r="F43" s="3">
-        <v>139000</v>
+        <v>142400</v>
       </c>
       <c r="G43" s="3">
-        <v>187400</v>
+        <v>192100</v>
       </c>
       <c r="H43" s="3">
-        <v>86600</v>
+        <v>88700</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1749,13 +1749,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>79900</v>
+        <v>81900</v>
       </c>
       <c r="E44" s="3">
-        <v>57200</v>
+        <v>58600</v>
       </c>
       <c r="F44" s="3">
-        <v>22200</v>
+        <v>22800</v>
       </c>
       <c r="G44" s="3">
         <v>400</v>
@@ -1782,19 +1782,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>40500</v>
+        <v>41500</v>
       </c>
       <c r="E45" s="3">
-        <v>13500</v>
+        <v>13900</v>
       </c>
       <c r="F45" s="3">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="G45" s="3">
-        <v>36900</v>
+        <v>37800</v>
       </c>
       <c r="H45" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1815,19 +1815,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4173200</v>
+        <v>4277100</v>
       </c>
       <c r="E46" s="3">
-        <v>4578800</v>
+        <v>4692700</v>
       </c>
       <c r="F46" s="3">
-        <v>5254200</v>
+        <v>5385000</v>
       </c>
       <c r="G46" s="3">
-        <v>5802700</v>
+        <v>5947100</v>
       </c>
       <c r="H46" s="3">
-        <v>6339300</v>
+        <v>6497100</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1848,19 +1848,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>152700</v>
+        <v>156500</v>
       </c>
       <c r="E47" s="3">
-        <v>129600</v>
+        <v>132800</v>
       </c>
       <c r="F47" s="3">
-        <v>137400</v>
+        <v>140900</v>
       </c>
       <c r="G47" s="3">
-        <v>174700</v>
+        <v>179000</v>
       </c>
       <c r="H47" s="3">
-        <v>100900</v>
+        <v>103500</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1881,19 +1881,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>136500</v>
+        <v>139900</v>
       </c>
       <c r="E48" s="3">
-        <v>166700</v>
+        <v>170800</v>
       </c>
       <c r="F48" s="3">
-        <v>148600</v>
+        <v>152300</v>
       </c>
       <c r="G48" s="3">
-        <v>111700</v>
+        <v>114500</v>
       </c>
       <c r="H48" s="3">
-        <v>71400</v>
+        <v>73200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1914,19 +1914,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>213400</v>
+        <v>218700</v>
       </c>
       <c r="E49" s="3">
-        <v>233600</v>
+        <v>239400</v>
       </c>
       <c r="F49" s="3">
-        <v>65000</v>
+        <v>66600</v>
       </c>
       <c r="G49" s="3">
-        <v>73000</v>
+        <v>74800</v>
       </c>
       <c r="H49" s="3">
-        <v>26900</v>
+        <v>27600</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2013,19 +2013,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>33300</v>
+        <v>34100</v>
       </c>
       <c r="E52" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="3">
-        <v>17100</v>
+        <v>17500</v>
       </c>
       <c r="H52" s="3">
-        <v>19800</v>
+        <v>20300</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2079,19 +2079,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4709000</v>
+        <v>4826300</v>
       </c>
       <c r="E54" s="3">
-        <v>5116400</v>
+        <v>5243800</v>
       </c>
       <c r="F54" s="3">
-        <v>5612200</v>
+        <v>5751900</v>
       </c>
       <c r="G54" s="3">
-        <v>6179200</v>
+        <v>6333000</v>
       </c>
       <c r="H54" s="3">
-        <v>6558300</v>
+        <v>6721600</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2142,19 +2142,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>145500</v>
+        <v>149100</v>
       </c>
       <c r="E57" s="3">
-        <v>159900</v>
+        <v>163900</v>
       </c>
       <c r="F57" s="3">
-        <v>148500</v>
+        <v>152200</v>
       </c>
       <c r="G57" s="3">
-        <v>186300</v>
+        <v>190900</v>
       </c>
       <c r="H57" s="3">
-        <v>155000</v>
+        <v>158900</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2175,19 +2175,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="E58" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="F58" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="G58" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="H58" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2208,19 +2208,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>312200</v>
+        <v>320000</v>
       </c>
       <c r="E59" s="3">
-        <v>397000</v>
+        <v>406800</v>
       </c>
       <c r="F59" s="3">
-        <v>455900</v>
+        <v>467200</v>
       </c>
       <c r="G59" s="3">
-        <v>493300</v>
+        <v>505600</v>
       </c>
       <c r="H59" s="3">
-        <v>456600</v>
+        <v>468000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2241,19 +2241,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>462800</v>
+        <v>474300</v>
       </c>
       <c r="E60" s="3">
-        <v>564700</v>
+        <v>578800</v>
       </c>
       <c r="F60" s="3">
-        <v>612200</v>
+        <v>627400</v>
       </c>
       <c r="G60" s="3">
-        <v>686500</v>
+        <v>703600</v>
       </c>
       <c r="H60" s="3">
-        <v>617900</v>
+        <v>633300</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2274,19 +2274,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="E61" s="3">
-        <v>15900</v>
+        <v>16300</v>
       </c>
       <c r="F61" s="3">
-        <v>21200</v>
+        <v>21800</v>
       </c>
       <c r="G61" s="3">
-        <v>24900</v>
+        <v>25500</v>
       </c>
       <c r="H61" s="3">
-        <v>21100</v>
+        <v>21700</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2307,19 +2307,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1219700</v>
+        <v>1250100</v>
       </c>
       <c r="E62" s="3">
-        <v>1806000</v>
+        <v>1850900</v>
       </c>
       <c r="F62" s="3">
-        <v>2122100</v>
+        <v>2175000</v>
       </c>
       <c r="G62" s="3">
-        <v>2581900</v>
+        <v>2646100</v>
       </c>
       <c r="H62" s="3">
-        <v>2811500</v>
+        <v>2881500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2439,19 +2439,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1687900</v>
+        <v>1729900</v>
       </c>
       <c r="E66" s="3">
-        <v>2386500</v>
+        <v>2445900</v>
       </c>
       <c r="F66" s="3">
-        <v>2755600</v>
+        <v>2824200</v>
       </c>
       <c r="G66" s="3">
-        <v>3293300</v>
+        <v>3375300</v>
       </c>
       <c r="H66" s="3">
-        <v>3450600</v>
+        <v>3536500</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2619,19 +2619,19 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-253100</v>
+        <v>-259400</v>
       </c>
       <c r="E72" s="3">
-        <v>-542000</v>
+        <v>-555500</v>
       </c>
       <c r="F72" s="3">
-        <v>-407800</v>
+        <v>-418000</v>
       </c>
       <c r="G72" s="3">
-        <v>-373500</v>
+        <v>-382800</v>
       </c>
       <c r="H72" s="3">
-        <v>-123300</v>
+        <v>-126300</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2751,19 +2751,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3021200</v>
+        <v>3096400</v>
       </c>
       <c r="E76" s="3">
-        <v>2729900</v>
+        <v>2797800</v>
       </c>
       <c r="F76" s="3">
-        <v>2856700</v>
+        <v>2927800</v>
       </c>
       <c r="G76" s="3">
-        <v>2885900</v>
+        <v>2957700</v>
       </c>
       <c r="H76" s="3">
-        <v>3107700</v>
+        <v>3185100</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2855,19 +2855,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>228800</v>
+        <v>234500</v>
       </c>
       <c r="E81" s="3">
-        <v>-235600</v>
+        <v>-241400</v>
       </c>
       <c r="F81" s="3">
-        <v>-111600</v>
+        <v>-114300</v>
       </c>
       <c r="G81" s="3">
-        <v>-330100</v>
+        <v>-338300</v>
       </c>
       <c r="H81" s="3">
-        <v>161900</v>
+        <v>166000</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2903,19 +2903,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>47200</v>
+        <v>48300</v>
       </c>
       <c r="E83" s="3">
-        <v>70900</v>
+        <v>72600</v>
       </c>
       <c r="F83" s="3">
-        <v>37400</v>
+        <v>38400</v>
       </c>
       <c r="G83" s="3">
-        <v>20200</v>
+        <v>20700</v>
       </c>
       <c r="H83" s="3">
-        <v>13500</v>
+        <v>13800</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3101,19 +3101,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-438700</v>
+        <v>-449700</v>
       </c>
       <c r="E89" s="3">
-        <v>-540900</v>
+        <v>-554400</v>
       </c>
       <c r="F89" s="3">
-        <v>-544500</v>
+        <v>-558000</v>
       </c>
       <c r="G89" s="3">
-        <v>-461800</v>
+        <v>-473300</v>
       </c>
       <c r="H89" s="3">
-        <v>3252600</v>
+        <v>3333500</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3149,19 +3149,19 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-20200</v>
+        <v>-20700</v>
       </c>
       <c r="E91" s="3">
-        <v>-29600</v>
+        <v>-30300</v>
       </c>
       <c r="F91" s="3">
-        <v>-58600</v>
+        <v>-60000</v>
       </c>
       <c r="G91" s="3">
-        <v>-46000</v>
+        <v>-47100</v>
       </c>
       <c r="H91" s="3">
-        <v>-24200</v>
+        <v>-24800</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3248,19 +3248,19 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>76900</v>
+        <v>78800</v>
       </c>
       <c r="E94" s="3">
-        <v>-1346000</v>
+        <v>-1379500</v>
       </c>
       <c r="F94" s="3">
-        <v>584900</v>
+        <v>599500</v>
       </c>
       <c r="G94" s="3">
-        <v>818400</v>
+        <v>838800</v>
       </c>
       <c r="H94" s="3">
-        <v>-4068500</v>
+        <v>-4169700</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3428,19 +3428,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5400</v>
+        <v>-5500</v>
       </c>
       <c r="E100" s="3">
         <v>-1600</v>
       </c>
       <c r="F100" s="3">
-        <v>-4200</v>
+        <v>-4300</v>
       </c>
       <c r="G100" s="3">
-        <v>23800</v>
+        <v>24400</v>
       </c>
       <c r="H100" s="3">
-        <v>1443500</v>
+        <v>1479500</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3461,19 +3461,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="E101" s="3">
-        <v>24100</v>
+        <v>24700</v>
       </c>
       <c r="F101" s="3">
-        <v>61300</v>
+        <v>62900</v>
       </c>
       <c r="G101" s="3">
-        <v>-76200</v>
+        <v>-78100</v>
       </c>
       <c r="H101" s="3">
-        <v>-10800</v>
+        <v>-11000</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3494,19 +3494,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-368900</v>
+        <v>-378000</v>
       </c>
       <c r="E102" s="3">
-        <v>-1864500</v>
+        <v>-1910900</v>
       </c>
       <c r="F102" s="3">
-        <v>97600</v>
+        <v>100000</v>
       </c>
       <c r="G102" s="3">
-        <v>304200</v>
+        <v>311700</v>
       </c>
       <c r="H102" s="3">
-        <v>616900</v>
+        <v>632200</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>GLPG</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -696,11 +696,11 @@
       <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>317900</v>
+        <v>265000</v>
       </c>
       <c r="E8" s="3">
-        <v>307200</v>
+        <v>257800</v>
       </c>
       <c r="F8" s="3">
-        <v>596500</v>
+        <v>266600</v>
       </c>
       <c r="G8" s="3">
-        <v>587300</v>
+        <v>584800</v>
       </c>
       <c r="H8" s="3">
-        <v>981100</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>936900</v>
+      </c>
+      <c r="I8" s="3">
+        <v>363900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>187200</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -747,26 +747,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>266700</v>
       </c>
       <c r="E9" s="3">
-        <v>13400</v>
+        <v>250200</v>
       </c>
       <c r="F9" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>364500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>640600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>471400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>369700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>262400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -780,26 +780,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-1700</v>
       </c>
       <c r="E10" s="3">
-        <v>293800</v>
+        <v>7600</v>
       </c>
       <c r="F10" s="3">
-        <v>594700</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>-97900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>465500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-75100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -829,25 +829,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>203600</v>
+        <v>266700</v>
       </c>
       <c r="E12" s="3">
-        <v>198100</v>
+        <v>288300</v>
       </c>
       <c r="F12" s="3">
-        <v>505300</v>
+        <v>364500</v>
       </c>
       <c r="G12" s="3">
-        <v>552000</v>
+        <v>640600</v>
       </c>
       <c r="H12" s="3">
-        <v>438600</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>471400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>371400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>262400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -895,22 +895,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24700</v>
+        <v>-33400</v>
       </c>
       <c r="E14" s="3">
-        <v>29600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>30700</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>201300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-2100</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>42500</v>
+        <v>25800</v>
       </c>
       <c r="E15" s="3">
-        <v>97300</v>
+        <v>17800</v>
       </c>
       <c r="F15" s="3">
-        <v>38400</v>
+        <v>9500</v>
       </c>
       <c r="G15" s="3">
-        <v>18800</v>
+        <v>9700</v>
       </c>
       <c r="H15" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>6200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4400</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>415600</v>
+        <v>354100</v>
       </c>
       <c r="E17" s="3">
-        <v>452400</v>
+        <v>359800</v>
       </c>
       <c r="F17" s="3">
-        <v>780000</v>
+        <v>461700</v>
       </c>
       <c r="G17" s="3">
-        <v>785200</v>
+        <v>803300</v>
       </c>
       <c r="H17" s="3">
-        <v>572700</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>523100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>415200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>295100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-97800</v>
+        <v>-89100</v>
       </c>
       <c r="E18" s="3">
-        <v>-145200</v>
+        <v>-101900</v>
       </c>
       <c r="F18" s="3">
-        <v>-183400</v>
+        <v>-195100</v>
       </c>
       <c r="G18" s="3">
-        <v>-197900</v>
+        <v>-218500</v>
       </c>
       <c r="H18" s="3">
-        <v>408400</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>413800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-107800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>106000</v>
+        <v>23800</v>
       </c>
       <c r="E20" s="3">
-        <v>74300</v>
+        <v>-45000</v>
       </c>
       <c r="F20" s="3">
-        <v>60100</v>
+        <v>-67200</v>
       </c>
       <c r="G20" s="3">
-        <v>-134900</v>
+        <v>161100</v>
       </c>
       <c r="H20" s="3">
-        <v>-242500</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>60500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>33400</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>56500</v>
+        <v>-87100</v>
       </c>
       <c r="E21" s="3">
-        <v>1800</v>
+        <v>-39100</v>
       </c>
       <c r="F21" s="3">
-        <v>-85000</v>
+        <v>-118500</v>
       </c>
       <c r="G21" s="3">
-        <v>-312000</v>
+        <v>-369900</v>
       </c>
       <c r="H21" s="3">
-        <v>179700</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>359500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-136900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1123,22 +1123,22 @@
         <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>7600</v>
+        <v>7400</v>
       </c>
       <c r="F22" s="3">
-        <v>12900</v>
+        <v>13200</v>
       </c>
       <c r="G22" s="3">
-        <v>10400</v>
+        <v>11500</v>
       </c>
       <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1156,22 +1156,22 @@
         <v>6200</v>
       </c>
       <c r="E23" s="3">
-        <v>-78500</v>
+        <v>-75700</v>
       </c>
       <c r="F23" s="3">
-        <v>-136200</v>
+        <v>-135800</v>
       </c>
       <c r="G23" s="3">
-        <v>-343100</v>
+        <v>-378900</v>
       </c>
       <c r="H23" s="3">
-        <v>164500</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>166700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-138700</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1192,19 +1192,19 @@
         <v>600</v>
       </c>
       <c r="F24" s="3">
-        <v>2700</v>
+        <v>1600</v>
       </c>
       <c r="G24" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>200</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1255,22 +1255,22 @@
         <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-79100</v>
+        <v>-76300</v>
       </c>
       <c r="F26" s="3">
+        <v>-137400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-380400</v>
+      </c>
+      <c r="H26" s="3">
+        <v>166900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-138900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>164700</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1285,25 +1285,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4400</v>
+        <v>234000</v>
       </c>
       <c r="E27" s="3">
-        <v>-79100</v>
+        <v>-233000</v>
       </c>
       <c r="F27" s="3">
+        <v>-117400</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-373600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>168200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-138900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>164700</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1351,25 +1351,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>238900</v>
+        <v>238400</v>
       </c>
       <c r="E29" s="3">
-        <v>-162300</v>
+        <v>-156600</v>
       </c>
       <c r="F29" s="3">
-        <v>24600</v>
+        <v>20000</v>
       </c>
       <c r="G29" s="3">
-        <v>6200</v>
+        <v>6800</v>
       </c>
       <c r="H29" s="3">
         <v>1300</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-106000</v>
+        <v>-23800</v>
       </c>
       <c r="E32" s="3">
-        <v>-74300</v>
+        <v>45000</v>
       </c>
       <c r="F32" s="3">
-        <v>-60100</v>
+        <v>67200</v>
       </c>
       <c r="G32" s="3">
-        <v>134900</v>
+        <v>-161100</v>
       </c>
       <c r="H32" s="3">
-        <v>242500</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-60500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-33400</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1483,25 +1483,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>234500</v>
+        <v>234000</v>
       </c>
       <c r="E33" s="3">
-        <v>-241400</v>
+        <v>-233000</v>
       </c>
       <c r="F33" s="3">
-        <v>-114300</v>
+        <v>-117400</v>
       </c>
       <c r="G33" s="3">
-        <v>-338300</v>
+        <v>-373600</v>
       </c>
       <c r="H33" s="3">
-        <v>166000</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>168200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-138900</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1549,25 +1549,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>234500</v>
+        <v>234000</v>
       </c>
       <c r="E35" s="3">
-        <v>-241400</v>
+        <v>-233000</v>
       </c>
       <c r="F35" s="3">
-        <v>-114300</v>
+        <v>-117400</v>
       </c>
       <c r="G35" s="3">
-        <v>-338300</v>
+        <v>-373600</v>
       </c>
       <c r="H35" s="3">
-        <v>166000</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>168200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-138900</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1601,11 +1601,11 @@
       <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>79500</v>
+        <v>184400</v>
       </c>
       <c r="E41" s="3">
-        <v>507400</v>
+        <v>543000</v>
       </c>
       <c r="F41" s="3">
-        <v>1357800</v>
+        <v>2539900</v>
       </c>
       <c r="G41" s="3">
-        <v>1373400</v>
+        <v>2611800</v>
       </c>
       <c r="H41" s="3">
-        <v>1005600</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>2089100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1477900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1382300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4001400</v>
+        <v>3888200</v>
       </c>
       <c r="E42" s="3">
-        <v>4027200</v>
+        <v>3832400</v>
       </c>
       <c r="F42" s="3">
-        <v>3851500</v>
+        <v>2808800</v>
       </c>
       <c r="G42" s="3">
-        <v>4343400</v>
+        <v>3701900</v>
       </c>
       <c r="H42" s="3">
-        <v>5397200</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>4398200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>72700</v>
+        <v>72600</v>
       </c>
       <c r="E43" s="3">
-        <v>85700</v>
+        <v>82700</v>
       </c>
       <c r="F43" s="3">
-        <v>142400</v>
+        <v>146300</v>
       </c>
       <c r="G43" s="3">
-        <v>192100</v>
+        <v>212100</v>
       </c>
       <c r="H43" s="3">
-        <v>88700</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>89900</v>
+      </c>
+      <c r="I43" s="3">
+        <v>38400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>50200</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1749,13 +1749,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>81900</v>
+        <v>81800</v>
       </c>
       <c r="E44" s="3">
-        <v>58600</v>
+        <v>56600</v>
       </c>
       <c r="F44" s="3">
-        <v>22800</v>
+        <v>23400</v>
       </c>
       <c r="G44" s="3">
         <v>400</v>
@@ -1763,11 +1763,11 @@
       <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="I44" s="3">
+        <v>300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>300</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1782,25 +1782,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G45" s="3">
         <v>41500</v>
       </c>
-      <c r="E45" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>37800</v>
-      </c>
       <c r="H45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>5000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>4600</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4277100</v>
+        <v>4268400</v>
       </c>
       <c r="E46" s="3">
-        <v>4692700</v>
+        <v>4528000</v>
       </c>
       <c r="F46" s="3">
-        <v>5385000</v>
+        <v>5529200</v>
       </c>
       <c r="G46" s="3">
-        <v>5947100</v>
+        <v>6568000</v>
       </c>
       <c r="H46" s="3">
-        <v>6497100</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>6582800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1521500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1438100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1848,25 +1848,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>156500</v>
-      </c>
-      <c r="E47" s="3">
-        <v>132800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>140900</v>
+        <v>15000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>179000</v>
+        <v>10900</v>
       </c>
       <c r="H47" s="3">
-        <v>103500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>12700</v>
+      </c>
+      <c r="I47" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>139900</v>
+        <v>139600</v>
       </c>
       <c r="E48" s="3">
-        <v>170800</v>
+        <v>164900</v>
       </c>
       <c r="F48" s="3">
-        <v>152300</v>
+        <v>156400</v>
       </c>
       <c r="G48" s="3">
-        <v>114500</v>
+        <v>126500</v>
       </c>
       <c r="H48" s="3">
-        <v>73200</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>74100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>26500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>20000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>218700</v>
+        <v>208600</v>
       </c>
       <c r="E49" s="3">
-        <v>239400</v>
+        <v>220100</v>
       </c>
       <c r="F49" s="3">
-        <v>66600</v>
+        <v>54900</v>
       </c>
       <c r="G49" s="3">
-        <v>74800</v>
+        <v>66300</v>
       </c>
       <c r="H49" s="3">
-        <v>27600</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>11300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>34100</v>
+        <v>173900</v>
       </c>
       <c r="E52" s="3">
-        <v>7900</v>
+        <v>134400</v>
       </c>
       <c r="F52" s="3">
-        <v>7200</v>
+        <v>147500</v>
       </c>
       <c r="G52" s="3">
-        <v>17500</v>
+        <v>139500</v>
       </c>
       <c r="H52" s="3">
-        <v>20300</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>108000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>86300</v>
+      </c>
+      <c r="J52" s="3">
+        <v>78900</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4826300</v>
+        <v>4816400</v>
       </c>
       <c r="E54" s="3">
-        <v>5243800</v>
+        <v>5059700</v>
       </c>
       <c r="F54" s="3">
-        <v>5751900</v>
+        <v>5906000</v>
       </c>
       <c r="G54" s="3">
-        <v>6333000</v>
+        <v>6994200</v>
       </c>
       <c r="H54" s="3">
-        <v>6721600</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>6810200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1648200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1544500</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>149100</v>
+        <v>148800</v>
       </c>
       <c r="E57" s="3">
-        <v>163900</v>
+        <v>142500</v>
       </c>
       <c r="F57" s="3">
-        <v>152200</v>
+        <v>152700</v>
       </c>
       <c r="G57" s="3">
-        <v>190900</v>
+        <v>209600</v>
       </c>
       <c r="H57" s="3">
-        <v>158900</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>159900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>77900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>56600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="E58" s="3">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="F58" s="3">
-        <v>8000</v>
+        <v>8200</v>
       </c>
       <c r="G58" s="3">
-        <v>7100</v>
+        <v>7800</v>
       </c>
       <c r="H58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>320000</v>
+        <v>318700</v>
       </c>
       <c r="E59" s="3">
-        <v>406800</v>
+        <v>407600</v>
       </c>
       <c r="F59" s="3">
-        <v>467200</v>
+        <v>479800</v>
       </c>
       <c r="G59" s="3">
-        <v>505600</v>
+        <v>558400</v>
       </c>
       <c r="H59" s="3">
-        <v>468000</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>474200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>172900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>148200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>474300</v>
+        <v>473300</v>
       </c>
       <c r="E60" s="3">
-        <v>578800</v>
+        <v>558400</v>
       </c>
       <c r="F60" s="3">
-        <v>627400</v>
+        <v>644200</v>
       </c>
       <c r="G60" s="3">
-        <v>703600</v>
+        <v>777100</v>
       </c>
       <c r="H60" s="3">
-        <v>633300</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>641700</v>
+      </c>
+      <c r="I60" s="3">
+        <v>251800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>206200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2277,16 +2277,16 @@
         <v>5500</v>
       </c>
       <c r="E61" s="3">
-        <v>16300</v>
+        <v>15700</v>
       </c>
       <c r="F61" s="3">
-        <v>21800</v>
+        <v>22400</v>
       </c>
       <c r="G61" s="3">
-        <v>25500</v>
+        <v>28200</v>
       </c>
       <c r="H61" s="3">
-        <v>21700</v>
+        <v>21900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1250100</v>
+        <v>34900</v>
       </c>
       <c r="E62" s="3">
-        <v>1850900</v>
+        <v>23300</v>
       </c>
       <c r="F62" s="3">
-        <v>2175000</v>
+        <v>8100</v>
       </c>
       <c r="G62" s="3">
-        <v>2646100</v>
+        <v>9900</v>
       </c>
       <c r="H62" s="3">
-        <v>2881500</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>7800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2000</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1729900</v>
+        <v>1726400</v>
       </c>
       <c r="E66" s="3">
-        <v>2445900</v>
+        <v>2360100</v>
       </c>
       <c r="F66" s="3">
-        <v>2824200</v>
+        <v>2899800</v>
       </c>
       <c r="G66" s="3">
-        <v>3375300</v>
+        <v>3727700</v>
       </c>
       <c r="H66" s="3">
-        <v>3536500</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>3583200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>257900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>329400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-259400</v>
+        <v>-252300</v>
       </c>
       <c r="E72" s="3">
-        <v>-555500</v>
+        <v>-530800</v>
       </c>
       <c r="F72" s="3">
-        <v>-418000</v>
+        <v>-417600</v>
       </c>
       <c r="G72" s="3">
-        <v>-382800</v>
+        <v>-409400</v>
       </c>
       <c r="H72" s="3">
-        <v>-126300</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>-122600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-340900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-253900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3096400</v>
+        <v>3090000</v>
       </c>
       <c r="E76" s="3">
-        <v>2797800</v>
+        <v>2699600</v>
       </c>
       <c r="F76" s="3">
-        <v>2927800</v>
+        <v>3006200</v>
       </c>
       <c r="G76" s="3">
-        <v>2957700</v>
+        <v>3266500</v>
       </c>
       <c r="H76" s="3">
-        <v>3185100</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>3227100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>1390300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1215200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2836,11 +2836,11 @@
       <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2855,25 +2855,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>234500</v>
+        <v>234000</v>
       </c>
       <c r="E81" s="3">
-        <v>-241400</v>
+        <v>-233000</v>
       </c>
       <c r="F81" s="3">
-        <v>-114300</v>
+        <v>-117400</v>
       </c>
       <c r="G81" s="3">
-        <v>-338300</v>
+        <v>-373600</v>
       </c>
       <c r="H81" s="3">
-        <v>166000</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>168200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-138900</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>48300</v>
+        <v>18900</v>
       </c>
       <c r="E83" s="3">
-        <v>72600</v>
+        <v>18900</v>
       </c>
       <c r="F83" s="3">
-        <v>38400</v>
+        <v>16100</v>
       </c>
       <c r="G83" s="3">
-        <v>20700</v>
+        <v>15400</v>
       </c>
       <c r="H83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>11700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-449700</v>
+        <v>-448700</v>
       </c>
       <c r="E89" s="3">
-        <v>-554400</v>
+        <v>-534900</v>
       </c>
       <c r="F89" s="3">
-        <v>-558000</v>
+        <v>-573000</v>
       </c>
       <c r="G89" s="3">
-        <v>-473300</v>
+        <v>-522700</v>
       </c>
       <c r="H89" s="3">
-        <v>3333500</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>3600700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-163100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-176500</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3152,22 +3152,22 @@
         <v>-20700</v>
       </c>
       <c r="E91" s="3">
-        <v>-30300</v>
+        <v>-29300</v>
       </c>
       <c r="F91" s="3">
-        <v>-60000</v>
+        <v>-61600</v>
       </c>
       <c r="G91" s="3">
-        <v>-47100</v>
+        <v>-52000</v>
       </c>
       <c r="H91" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-25100</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-6400</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>78800</v>
+        <v>78700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1379500</v>
+        <v>-1331100</v>
       </c>
       <c r="F94" s="3">
-        <v>599500</v>
+        <v>615500</v>
       </c>
       <c r="G94" s="3">
-        <v>838800</v>
+        <v>926300</v>
       </c>
       <c r="H94" s="3">
-        <v>-4169700</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-4224700</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3434,19 +3434,19 @@
         <v>-1600</v>
       </c>
       <c r="F100" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="G100" s="3">
-        <v>24400</v>
+        <v>27000</v>
       </c>
       <c r="H100" s="3">
-        <v>1479500</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>1499000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>329600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>424300</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3464,22 +3464,22 @@
         <v>-1700</v>
       </c>
       <c r="E101" s="3">
-        <v>24700</v>
+        <v>23800</v>
       </c>
       <c r="F101" s="3">
-        <v>62900</v>
+        <v>64600</v>
       </c>
       <c r="G101" s="3">
-        <v>-78100</v>
+        <v>-86300</v>
       </c>
       <c r="H101" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-11200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-33400</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-378000</v>
+        <v>-377300</v>
       </c>
       <c r="E102" s="3">
-        <v>-1910900</v>
+        <v>-1843800</v>
       </c>
       <c r="F102" s="3">
-        <v>100000</v>
+        <v>102700</v>
       </c>
       <c r="G102" s="3">
-        <v>311700</v>
+        <v>344300</v>
       </c>
       <c r="H102" s="3">
-        <v>632200</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>863800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>159800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>213700</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>GLPG</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>285400</v>
+      </c>
+      <c r="E8" s="3">
         <v>265000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>257800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>266600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>584800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>936900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>363900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>187200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>383400</v>
+      </c>
+      <c r="E9" s="3">
         <v>266700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>250200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>364500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>640600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>471400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>369700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>262400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-97900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-55800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>465500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-75100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>347300</v>
+      </c>
+      <c r="E12" s="3">
         <v>266700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>288300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>364500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>640600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>471400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>371400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>262400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-76300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-33400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>30700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>201300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E15" s="3">
         <v>25800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>480400</v>
+      </c>
+      <c r="E17" s="3">
         <v>354100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>359800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>461700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>803300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>523100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>415200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>295100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-89100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-101900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-195100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-218500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>413800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-51300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-107800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E20" s="3">
         <v>23800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-45000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-67200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>161100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>60500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>33400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-134500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-87100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-118500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-369900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>359500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-35600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-136900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
         <v>6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-75700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-135800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-378900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>166700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-138700</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>10600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-76300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-137400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-380400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>166900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-138900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E27" s="3">
         <v>234000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-233000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-117400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-373600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>168200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-138900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,42 +1401,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E29" s="3">
         <v>238400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-156600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>20000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>6800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1300</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-23800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>45000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>67200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-161100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-60500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-33400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E33" s="3">
         <v>234000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-233000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-117400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-373600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>168200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-138900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E35" s="3">
         <v>234000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-233000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-117400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-373600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>168200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-138900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,124 +1729,134 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E41" s="3">
         <v>184400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>543000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2539900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2611800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2089100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1477900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1382300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3161100</v>
+      </c>
+      <c r="E42" s="3">
         <v>3888200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3832400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2808800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3701900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4398200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E43" s="3">
         <v>72600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>146300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>212100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>89900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>38400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E44" s="3">
         <v>81800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>56600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
-      </c>
-      <c r="H44" s="3">
-        <v>300</v>
       </c>
       <c r="I44" s="3">
         <v>300</v>
@@ -1769,180 +1864,198 @@
       <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>300</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E45" s="3">
         <v>40600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3457300</v>
+      </c>
+      <c r="E46" s="3">
         <v>4268400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4528000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5529200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6568000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6582800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1521500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1438100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E47" s="3">
         <v>15000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>10900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E48" s="3">
         <v>139600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>164900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>156400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>126500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>243200</v>
+      </c>
+      <c r="E49" s="3">
         <v>208600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>220100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>54900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>66300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E52" s="3">
         <v>173900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>134400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>147500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>139500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>108000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>86300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>78900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4281700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4816400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5059700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5906000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6994200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6810200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1648200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1544500</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,161 +2265,174 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E57" s="3">
         <v>148800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>142500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>152700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>209600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>159900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>77900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>240900</v>
+      </c>
+      <c r="E59" s="3">
         <v>318700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>407600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>479800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>558400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>474200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>172900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>148200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>346900</v>
+      </c>
+      <c r="E60" s="3">
         <v>473300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>558400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>644200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>777100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>641700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>251800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>206200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E61" s="3">
         <v>5500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2300,42 +2442,48 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E62" s="3">
         <v>34900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1282500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1726400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2360100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2899800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3727700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3583200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>257900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>329400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-252300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-530800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-417600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-409400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-122600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-340900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-253900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2999200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3090000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2699600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3006200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3266500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3227100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1390300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1215200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E81" s="3">
         <v>234000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-233000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-117400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-373600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>168200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-138900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18900</v>
+        <v>36600</v>
       </c>
       <c r="E83" s="3">
         <v>18900</v>
       </c>
       <c r="F83" s="3">
+        <v>18900</v>
+      </c>
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-331300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-448700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-534900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-573000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-522700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3600700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-163100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-176500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-61600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>228400</v>
+      </c>
+      <c r="E94" s="3">
         <v>78700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1331100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>615500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>926300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4224700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1499000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>329600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>424300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>23800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>64600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-86300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-11200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-377300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1843800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>102700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>344300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>863800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>159800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>213700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>GLPG</t>
   </si>
@@ -754,13 +754,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>383400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>266700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>250200</v>
+        <v>36100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>364500</v>
@@ -790,13 +790,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-98000</v>
+        <v>249300</v>
       </c>
       <c r="E10" s="3">
-        <v>-1700</v>
+        <v>265000</v>
       </c>
       <c r="F10" s="3">
-        <v>7600</v>
+        <v>257800</v>
       </c>
       <c r="G10" s="3">
         <v>-97900</v>
@@ -914,13 +914,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-76300</v>
+        <v>-75100</v>
       </c>
       <c r="E14" s="3">
-        <v>-33400</v>
+        <v>-30000</v>
       </c>
       <c r="F14" s="3">
-        <v>30700</v>
+        <v>-7400</v>
       </c>
       <c r="G14" s="3">
         <v>-2100</v>
@@ -950,13 +950,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>36600</v>
+        <v>35000</v>
       </c>
       <c r="E15" s="3">
         <v>25800</v>
       </c>
       <c r="F15" s="3">
-        <v>17800</v>
+        <v>70100</v>
       </c>
       <c r="G15" s="3">
         <v>9500</v>
@@ -999,13 +999,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>480400</v>
+        <v>479100</v>
       </c>
       <c r="E17" s="3">
-        <v>354100</v>
+        <v>350600</v>
       </c>
       <c r="F17" s="3">
-        <v>359800</v>
+        <v>397900</v>
       </c>
       <c r="G17" s="3">
         <v>461700</v>
@@ -1035,13 +1035,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-195000</v>
+        <v>-193700</v>
       </c>
       <c r="E18" s="3">
-        <v>-89100</v>
+        <v>-85600</v>
       </c>
       <c r="F18" s="3">
-        <v>-101900</v>
+        <v>-140100</v>
       </c>
       <c r="G18" s="3">
         <v>-195100</v>
@@ -1123,13 +1123,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-134500</v>
+        <v>-134900</v>
       </c>
       <c r="E21" s="3">
-        <v>-87100</v>
+        <v>-83600</v>
       </c>
       <c r="F21" s="3">
-        <v>-39100</v>
+        <v>-25000</v>
       </c>
       <c r="G21" s="3">
         <v>-118500</v>
@@ -1158,8 +1158,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>900</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
@@ -1808,7 +1808,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>90400</v>
+        <v>91200</v>
       </c>
       <c r="E43" s="3">
         <v>72600</v>
@@ -1880,7 +1880,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>86300</v>
+        <v>42800</v>
       </c>
       <c r="E45" s="3">
         <v>40600</v>
@@ -2024,7 +2024,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>243200</v>
+        <v>235700</v>
       </c>
       <c r="E49" s="3">
         <v>208600</v>
@@ -2272,7 +2272,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>102400</v>
+        <v>101200</v>
       </c>
       <c r="E57" s="3">
         <v>148800</v>
@@ -3101,13 +3101,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>36600</v>
+        <v>16200</v>
       </c>
       <c r="E83" s="3">
         <v>18900</v>
       </c>
       <c r="F83" s="3">
-        <v>18900</v>
+        <v>70100</v>
       </c>
       <c r="G83" s="3">
         <v>16100</v>

--- a/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLPG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>GLPG</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1305900</v>
+      </c>
+      <c r="E8" s="3">
         <v>285400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>265000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>257800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>266600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>584800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>936900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>363900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>555200</v>
+      </c>
+      <c r="E9" s="3">
         <v>383400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>266700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>288300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>364500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>640600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>471400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>369700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>262400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>750700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-98000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-30500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-97900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-55800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>465500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-5800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-75100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>539400</v>
+      </c>
+      <c r="E12" s="3">
         <v>347300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>266700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>288300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>364500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>640600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>471400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>371400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>262400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-75100</v>
-      </c>
-      <c r="E14" s="3">
+        <v>282900</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-30000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>201300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>35000</v>
+        <v>49800</v>
       </c>
       <c r="E15" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F15" s="3">
         <v>25800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>70100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>479100</v>
+        <v>698100</v>
       </c>
       <c r="E17" s="3">
+        <v>480400</v>
+      </c>
+      <c r="F17" s="3">
         <v>350600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>397900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>461700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>803300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>523100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>415200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>295100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-193700</v>
+        <v>607800</v>
       </c>
       <c r="E18" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-85600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-140100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-195100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-218500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>413800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-51300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-107800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,188 +1113,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-23900</v>
+        <v>24900</v>
       </c>
       <c r="E20" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="F20" s="3">
         <v>23800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-67200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>161100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>60500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>33400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-134900</v>
+        <v>632700</v>
       </c>
       <c r="E21" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-83600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-25000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-118500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-369900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>359500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-35600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-136900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>13200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>11500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>900</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>353300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-75700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-135800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-378900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>166700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-138700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>375100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-76300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-137400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-380400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>166900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-138900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E27" s="3">
         <v>76700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>234000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-233000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-117400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-373600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>168200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-138900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,45 +1461,51 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E29" s="3">
         <v>78000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>238400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-156600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>20000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>6800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1300</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23900</v>
+        <v>-24900</v>
       </c>
       <c r="E32" s="3">
+        <v>100200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-23800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>67200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-161100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-60500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-33400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E33" s="3">
         <v>76700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>234000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-233000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-117400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-373600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>168200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-138900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E35" s="3">
         <v>76700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>234000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-233000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-117400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-373600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>168200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-138900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,136 +1815,146 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E41" s="3">
         <v>66500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>184400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>543000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2539900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2611800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2089100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1477900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1382300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3416900</v>
+      </c>
+      <c r="E42" s="3">
         <v>3161100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3888200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3832400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2808800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3701900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4398200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>91200</v>
+        <v>61000</v>
       </c>
       <c r="E43" s="3">
+        <v>90400</v>
+      </c>
+      <c r="F43" s="3">
         <v>72600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>146300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>212100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>89900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E44" s="3">
         <v>53000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>81800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>56600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
-      </c>
-      <c r="I44" s="3">
-        <v>300</v>
       </c>
       <c r="J44" s="3">
         <v>300</v>
@@ -1867,195 +1962,213 @@
       <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>300</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42800</v>
+        <v>8200</v>
       </c>
       <c r="E45" s="3">
+        <v>86300</v>
+      </c>
+      <c r="F45" s="3">
         <v>40600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3615700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3457300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4268400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4528000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5529200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6568000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6582800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1521500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1438100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E47" s="3">
         <v>262100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>10900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E48" s="3">
         <v>127200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>139600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>164900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>156400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>126500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>74100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>235700</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
+        <v>243200</v>
+      </c>
+      <c r="F49" s="3">
         <v>208600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>220100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>54900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>66300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>208300</v>
+      </c>
+      <c r="E52" s="3">
         <v>190400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>173900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>134400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>147500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>108000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>78900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3999700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4281700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4816400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5059700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5906000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6994200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6810200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1648200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1544500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,176 +2395,189 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>101200</v>
+        <v>122900</v>
       </c>
       <c r="E57" s="3">
+        <v>102400</v>
+      </c>
+      <c r="F57" s="3">
         <v>148800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>142500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>152700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>209600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>159900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>77900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E59" s="3">
         <v>240900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>318700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>407600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>479800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>558400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>474200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>172900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>148200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E60" s="3">
         <v>346900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>473300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>558400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>644200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>777100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>641700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>251800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>206200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E61" s="3">
         <v>8500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2445,45 +2587,51 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E62" s="3">
         <v>35000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1282500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1726400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2360100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2899800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3727700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3583200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>257900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>329400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-139000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-252300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-530800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-417600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-409400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-122600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-340900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-253900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3799300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2999200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3090000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2699600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3006200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3266500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3227100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1390300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1215200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E81" s="3">
         <v>76700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>234000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-233000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-117400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-373600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>168200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-138900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16200</v>
+        <v>49800</v>
       </c>
       <c r="E83" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F83" s="3">
         <v>18900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>70100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-302300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-331300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-448700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-534900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-573000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-522700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3600700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-163100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-176500</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>339100</v>
+      </c>
+      <c r="E94" s="3">
         <v>228400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>78700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1331100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>615500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>926300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4224700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1499000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>329600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>424300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>64600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-86300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-106200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-377300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1843800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>102700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>344300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>863800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>159800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>213700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
